--- a/payroll_data.xlsx
+++ b/payroll_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\navee\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d9902cb691d738b/Documents/GitHub/Payroll_Chatbot/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D62CF7-92C9-4683-BCC6-11FCF0EC8F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOP Tracker" sheetId="1" r:id="rId1"/>
@@ -1549,7 +1549,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1605,7 +1605,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
